--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9986,6 +9986,4022 @@
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120318834</v>
+      </c>
+      <c r="B78" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>515221</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6924386</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120318829</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>515142</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6924327</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120318823</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>515067</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6924720</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120318815</v>
+      </c>
+      <c r="B81" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>514859</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6924782</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120318842</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>515405</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6924637</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120318827</v>
+      </c>
+      <c r="B83" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>515136</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6924416</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120318821</v>
+      </c>
+      <c r="B84" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>514957</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6924623</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120318847</v>
+      </c>
+      <c r="B85" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>515636</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6924856</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120318843</v>
+      </c>
+      <c r="B86" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>515289</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6924796</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>120318836</v>
+      </c>
+      <c r="B87" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>515223</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6924414</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>120318845</v>
+      </c>
+      <c r="B88" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>515553</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6924626</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>120318848</v>
+      </c>
+      <c r="B89" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>515521</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6924943</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120318817</v>
+      </c>
+      <c r="B90" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>514849</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6924760</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120318833</v>
+      </c>
+      <c r="B91" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>515213</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6924361</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120318844</v>
+      </c>
+      <c r="B92" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>515557</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6924620</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120318839</v>
+      </c>
+      <c r="B93" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>515335</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6924502</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120318832</v>
+      </c>
+      <c r="B94" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>515203</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6924357</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>120318813</v>
+      </c>
+      <c r="B95" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>514992</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6924909</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>120318841</v>
+      </c>
+      <c r="B96" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>515403</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6924623</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>120318819</v>
+      </c>
+      <c r="B97" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>514895</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6924584</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>120318852</v>
+      </c>
+      <c r="B98" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>515293</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6925084</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>120318846</v>
+      </c>
+      <c r="B99" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>515647</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6924817</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>120318840</v>
+      </c>
+      <c r="B100" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>514998</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6924990</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>120318818</v>
+      </c>
+      <c r="B101" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>514820</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6924711</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>120318831</v>
+      </c>
+      <c r="B102" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>515187</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6924328</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>120318814</v>
+      </c>
+      <c r="B103" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>514909</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6924793</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>120318835</v>
+      </c>
+      <c r="B104" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>515229</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6924387</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>120318825</v>
+      </c>
+      <c r="B105" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>515094</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6924722</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>120318828</v>
+      </c>
+      <c r="B106" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>515127</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6924384</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>120318826</v>
+      </c>
+      <c r="B107" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>515119</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6924734</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>120318822</v>
+      </c>
+      <c r="B108" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>515056</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6924723</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>120318812</v>
+      </c>
+      <c r="B109" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>515007</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6924912</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>120318824</v>
+      </c>
+      <c r="B110" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>515085</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6924717</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>120318820</v>
+      </c>
+      <c r="B111" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>514913</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6924578</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>120318837</v>
+      </c>
+      <c r="B112" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>515326</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6924467</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>120318830</v>
+      </c>
+      <c r="B113" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>515149</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6924307</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>120318849</v>
+      </c>
+      <c r="B114" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>515497</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6924983</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>120318816</v>
+      </c>
+      <c r="B115" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>514838</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6924796</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -9988,10 +9988,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120318834</v>
+        <v>120318839</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515221</v>
+        <v>515335</v>
       </c>
       <c r="R78" t="n">
-        <v>6924386</v>
+        <v>6924502</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10094,10 +10094,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120318829</v>
+        <v>120318836</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515142</v>
+        <v>515223</v>
       </c>
       <c r="R79" t="n">
-        <v>6924327</v>
+        <v>6924414</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10200,10 +10200,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120318823</v>
+        <v>120318843</v>
       </c>
       <c r="B80" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10233,21 +10233,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515067</v>
+        <v>515289</v>
       </c>
       <c r="R80" t="n">
-        <v>6924720</v>
+        <v>6924796</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10274,12 +10270,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10306,10 +10302,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120318815</v>
+        <v>120318834</v>
       </c>
       <c r="B81" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10341,7 +10337,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10350,10 +10346,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>514859</v>
+        <v>515221</v>
       </c>
       <c r="R81" t="n">
-        <v>6924782</v>
+        <v>6924386</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10412,10 +10408,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120318842</v>
+        <v>120318821</v>
       </c>
       <c r="B82" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10447,7 +10443,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10456,10 +10452,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515405</v>
+        <v>514957</v>
       </c>
       <c r="R82" t="n">
-        <v>6924637</v>
+        <v>6924623</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10518,10 +10514,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120318827</v>
+        <v>120318840</v>
       </c>
       <c r="B83" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10551,21 +10547,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515136</v>
+        <v>514998</v>
       </c>
       <c r="R83" t="n">
-        <v>6924416</v>
+        <v>6924990</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10592,12 +10584,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10624,10 +10616,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120318821</v>
+        <v>120318814</v>
       </c>
       <c r="B84" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10659,7 +10651,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>380</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10668,10 +10660,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>514957</v>
+        <v>514909</v>
       </c>
       <c r="R84" t="n">
-        <v>6924623</v>
+        <v>6924793</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10730,10 +10722,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120318847</v>
+        <v>120318841</v>
       </c>
       <c r="B85" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10765,7 +10757,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10774,10 +10766,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515636</v>
+        <v>515403</v>
       </c>
       <c r="R85" t="n">
-        <v>6924856</v>
+        <v>6924623</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10836,10 +10828,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120318843</v>
+        <v>120318845</v>
       </c>
       <c r="B86" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10869,17 +10861,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515289</v>
+        <v>515553</v>
       </c>
       <c r="R86" t="n">
-        <v>6924796</v>
+        <v>6924626</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10906,12 +10902,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10938,10 +10934,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120318836</v>
+        <v>120318825</v>
       </c>
       <c r="B87" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10973,7 +10969,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10982,10 +10978,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515223</v>
+        <v>515094</v>
       </c>
       <c r="R87" t="n">
-        <v>6924414</v>
+        <v>6924722</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11044,10 +11040,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120318845</v>
+        <v>120318817</v>
       </c>
       <c r="B88" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11079,7 +11075,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11088,10 +11084,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>515553</v>
+        <v>514849</v>
       </c>
       <c r="R88" t="n">
-        <v>6924626</v>
+        <v>6924760</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11150,10 +11146,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120318848</v>
+        <v>120318812</v>
       </c>
       <c r="B89" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11185,7 +11181,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11194,10 +11190,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>515521</v>
+        <v>515007</v>
       </c>
       <c r="R89" t="n">
-        <v>6924943</v>
+        <v>6924912</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11256,10 +11252,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120318817</v>
+        <v>120318822</v>
       </c>
       <c r="B90" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11291,7 +11287,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11300,10 +11296,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>514849</v>
+        <v>515056</v>
       </c>
       <c r="R90" t="n">
-        <v>6924760</v>
+        <v>6924723</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11362,10 +11358,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120318833</v>
+        <v>120318844</v>
       </c>
       <c r="B91" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11397,7 +11393,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11406,10 +11402,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>515213</v>
+        <v>515557</v>
       </c>
       <c r="R91" t="n">
-        <v>6924361</v>
+        <v>6924620</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11468,10 +11464,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120318844</v>
+        <v>120318830</v>
       </c>
       <c r="B92" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11503,7 +11499,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11512,10 +11508,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>515557</v>
+        <v>515149</v>
       </c>
       <c r="R92" t="n">
-        <v>6924620</v>
+        <v>6924307</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11574,10 +11570,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120318839</v>
+        <v>120318829</v>
       </c>
       <c r="B93" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11609,7 +11605,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11618,10 +11614,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>515335</v>
+        <v>515142</v>
       </c>
       <c r="R93" t="n">
-        <v>6924502</v>
+        <v>6924327</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11680,10 +11676,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120318832</v>
+        <v>120318831</v>
       </c>
       <c r="B94" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11715,7 +11711,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11724,10 +11720,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>515203</v>
+        <v>515187</v>
       </c>
       <c r="R94" t="n">
-        <v>6924357</v>
+        <v>6924328</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11786,10 +11782,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120318813</v>
+        <v>120318827</v>
       </c>
       <c r="B95" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11821,7 +11817,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11830,10 +11826,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>514992</v>
+        <v>515136</v>
       </c>
       <c r="R95" t="n">
-        <v>6924909</v>
+        <v>6924416</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11892,10 +11888,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120318841</v>
+        <v>120318823</v>
       </c>
       <c r="B96" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11927,7 +11923,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11936,10 +11932,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>515403</v>
+        <v>515067</v>
       </c>
       <c r="R96" t="n">
-        <v>6924623</v>
+        <v>6924720</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11998,10 +11994,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120318819</v>
+        <v>120318848</v>
       </c>
       <c r="B97" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12033,7 +12029,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12042,10 +12038,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>514895</v>
+        <v>515521</v>
       </c>
       <c r="R97" t="n">
-        <v>6924584</v>
+        <v>6924943</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12104,10 +12100,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120318852</v>
+        <v>120318818</v>
       </c>
       <c r="B98" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12137,17 +12133,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>515293</v>
+        <v>514820</v>
       </c>
       <c r="R98" t="n">
-        <v>6925084</v>
+        <v>6924711</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12174,12 +12174,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12206,10 +12206,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120318846</v>
+        <v>120318832</v>
       </c>
       <c r="B99" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12250,10 +12250,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>515647</v>
+        <v>515203</v>
       </c>
       <c r="R99" t="n">
-        <v>6924817</v>
+        <v>6924357</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12312,10 +12312,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120318840</v>
+        <v>120318815</v>
       </c>
       <c r="B100" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12345,17 +12345,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>514998</v>
+        <v>514859</v>
       </c>
       <c r="R100" t="n">
-        <v>6924990</v>
+        <v>6924782</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12382,12 +12386,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12414,10 +12418,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120318818</v>
+        <v>120318847</v>
       </c>
       <c r="B101" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12449,7 +12453,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12458,10 +12462,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>514820</v>
+        <v>515636</v>
       </c>
       <c r="R101" t="n">
-        <v>6924711</v>
+        <v>6924856</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12520,10 +12524,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120318831</v>
+        <v>120318852</v>
       </c>
       <c r="B102" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12553,21 +12557,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>515187</v>
+        <v>515293</v>
       </c>
       <c r="R102" t="n">
-        <v>6924328</v>
+        <v>6925084</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12594,12 +12594,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12626,10 +12626,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120318814</v>
+        <v>120318820</v>
       </c>
       <c r="B103" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12670,10 +12670,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>514909</v>
+        <v>514913</v>
       </c>
       <c r="R103" t="n">
-        <v>6924793</v>
+        <v>6924578</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12732,10 +12732,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120318835</v>
+        <v>120318833</v>
       </c>
       <c r="B104" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12776,10 +12776,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>515229</v>
+        <v>515213</v>
       </c>
       <c r="R104" t="n">
-        <v>6924387</v>
+        <v>6924361</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12838,10 +12838,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120318825</v>
+        <v>120318826</v>
       </c>
       <c r="B105" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>515094</v>
+        <v>515119</v>
       </c>
       <c r="R105" t="n">
-        <v>6924722</v>
+        <v>6924734</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12947,7 +12947,7 @@
         <v>120318828</v>
       </c>
       <c r="B106" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13050,10 +13050,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120318826</v>
+        <v>120318824</v>
       </c>
       <c r="B107" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13094,10 +13094,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>515119</v>
+        <v>515085</v>
       </c>
       <c r="R107" t="n">
-        <v>6924734</v>
+        <v>6924717</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13156,10 +13156,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120318822</v>
+        <v>120318849</v>
       </c>
       <c r="B108" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -13200,10 +13200,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>515056</v>
+        <v>515497</v>
       </c>
       <c r="R108" t="n">
-        <v>6924723</v>
+        <v>6924983</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13262,10 +13262,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120318812</v>
+        <v>120318816</v>
       </c>
       <c r="B109" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -13306,10 +13306,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>515007</v>
+        <v>514838</v>
       </c>
       <c r="R109" t="n">
-        <v>6924912</v>
+        <v>6924796</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13368,10 +13368,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120318824</v>
+        <v>120318835</v>
       </c>
       <c r="B110" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13412,10 +13412,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>515085</v>
+        <v>515229</v>
       </c>
       <c r="R110" t="n">
-        <v>6924717</v>
+        <v>6924387</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13474,10 +13474,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120318820</v>
+        <v>120318819</v>
       </c>
       <c r="B111" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13518,10 +13518,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>514913</v>
+        <v>514895</v>
       </c>
       <c r="R111" t="n">
-        <v>6924578</v>
+        <v>6924584</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13583,7 +13583,7 @@
         <v>120318837</v>
       </c>
       <c r="B112" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13686,10 +13686,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120318830</v>
+        <v>120318813</v>
       </c>
       <c r="B113" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13730,10 +13730,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>515149</v>
+        <v>514992</v>
       </c>
       <c r="R113" t="n">
-        <v>6924307</v>
+        <v>6924909</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13792,10 +13792,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120318849</v>
+        <v>120318842</v>
       </c>
       <c r="B114" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13836,10 +13836,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>515497</v>
+        <v>515405</v>
       </c>
       <c r="R114" t="n">
-        <v>6924983</v>
+        <v>6924637</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13898,10 +13898,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120318816</v>
+        <v>120318846</v>
       </c>
       <c r="B115" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>514838</v>
+        <v>515647</v>
       </c>
       <c r="R115" t="n">
-        <v>6924796</v>
+        <v>6924817</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -9988,7 +9988,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120318839</v>
+        <v>120318833</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515335</v>
+        <v>515213</v>
       </c>
       <c r="R78" t="n">
-        <v>6924502</v>
+        <v>6924361</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120318836</v>
+        <v>120318843</v>
       </c>
       <c r="B79" t="n">
         <v>97930</v>
@@ -10127,21 +10127,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515223</v>
+        <v>515289</v>
       </c>
       <c r="R79" t="n">
-        <v>6924414</v>
+        <v>6924796</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10168,12 +10164,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10200,7 +10196,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120318843</v>
+        <v>120318817</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -10233,17 +10229,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515289</v>
+        <v>514849</v>
       </c>
       <c r="R80" t="n">
-        <v>6924796</v>
+        <v>6924760</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10270,12 +10270,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10302,7 +10302,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120318834</v>
+        <v>120318828</v>
       </c>
       <c r="B81" t="n">
         <v>97930</v>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515221</v>
+        <v>515127</v>
       </c>
       <c r="R81" t="n">
-        <v>6924386</v>
+        <v>6924384</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10408,7 +10408,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120318821</v>
+        <v>120318819</v>
       </c>
       <c r="B82" t="n">
         <v>97930</v>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>514957</v>
+        <v>514895</v>
       </c>
       <c r="R82" t="n">
-        <v>6924623</v>
+        <v>6924584</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10514,7 +10514,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120318840</v>
+        <v>120318841</v>
       </c>
       <c r="B83" t="n">
         <v>97930</v>
@@ -10547,17 +10547,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>514998</v>
+        <v>515403</v>
       </c>
       <c r="R83" t="n">
-        <v>6924990</v>
+        <v>6924623</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10584,12 +10588,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10616,7 +10620,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120318814</v>
+        <v>120318825</v>
       </c>
       <c r="B84" t="n">
         <v>97930</v>
@@ -10651,7 +10655,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10660,10 +10664,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>514909</v>
+        <v>515094</v>
       </c>
       <c r="R84" t="n">
-        <v>6924793</v>
+        <v>6924722</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10722,7 +10726,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120318841</v>
+        <v>120318830</v>
       </c>
       <c r="B85" t="n">
         <v>97930</v>
@@ -10757,7 +10761,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10766,10 +10770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515403</v>
+        <v>515149</v>
       </c>
       <c r="R85" t="n">
-        <v>6924623</v>
+        <v>6924307</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10828,7 +10832,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120318845</v>
+        <v>120318835</v>
       </c>
       <c r="B86" t="n">
         <v>97930</v>
@@ -10863,7 +10867,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10872,10 +10876,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515553</v>
+        <v>515229</v>
       </c>
       <c r="R86" t="n">
-        <v>6924626</v>
+        <v>6924387</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10934,7 +10938,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120318825</v>
+        <v>120318818</v>
       </c>
       <c r="B87" t="n">
         <v>97930</v>
@@ -10969,7 +10973,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10978,10 +10982,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515094</v>
+        <v>514820</v>
       </c>
       <c r="R87" t="n">
-        <v>6924722</v>
+        <v>6924711</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11040,7 +11044,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120318817</v>
+        <v>120318815</v>
       </c>
       <c r="B88" t="n">
         <v>97930</v>
@@ -11075,7 +11079,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11084,10 +11088,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>514849</v>
+        <v>514859</v>
       </c>
       <c r="R88" t="n">
-        <v>6924760</v>
+        <v>6924782</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11146,7 +11150,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120318812</v>
+        <v>120318820</v>
       </c>
       <c r="B89" t="n">
         <v>97930</v>
@@ -11181,7 +11185,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11190,10 +11194,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>515007</v>
+        <v>514913</v>
       </c>
       <c r="R89" t="n">
-        <v>6924912</v>
+        <v>6924578</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11252,7 +11256,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120318822</v>
+        <v>120318836</v>
       </c>
       <c r="B90" t="n">
         <v>97930</v>
@@ -11287,7 +11291,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11296,10 +11300,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>515056</v>
+        <v>515223</v>
       </c>
       <c r="R90" t="n">
-        <v>6924723</v>
+        <v>6924414</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11358,7 +11362,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120318844</v>
+        <v>120318814</v>
       </c>
       <c r="B91" t="n">
         <v>97930</v>
@@ -11393,7 +11397,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>380</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11402,10 +11406,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>515557</v>
+        <v>514909</v>
       </c>
       <c r="R91" t="n">
-        <v>6924620</v>
+        <v>6924793</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11464,7 +11468,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120318830</v>
+        <v>120318813</v>
       </c>
       <c r="B92" t="n">
         <v>97930</v>
@@ -11499,7 +11503,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11508,10 +11512,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>515149</v>
+        <v>514992</v>
       </c>
       <c r="R92" t="n">
-        <v>6924307</v>
+        <v>6924909</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11570,7 +11574,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120318829</v>
+        <v>120318816</v>
       </c>
       <c r="B93" t="n">
         <v>97930</v>
@@ -11605,7 +11609,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11614,10 +11618,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>515142</v>
+        <v>514838</v>
       </c>
       <c r="R93" t="n">
-        <v>6924327</v>
+        <v>6924796</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11676,7 +11680,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120318831</v>
+        <v>120318839</v>
       </c>
       <c r="B94" t="n">
         <v>97930</v>
@@ -11711,7 +11715,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11720,10 +11724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>515187</v>
+        <v>515335</v>
       </c>
       <c r="R94" t="n">
-        <v>6924328</v>
+        <v>6924502</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11782,7 +11786,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120318827</v>
+        <v>120318849</v>
       </c>
       <c r="B95" t="n">
         <v>97930</v>
@@ -11817,7 +11821,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11826,10 +11830,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>515136</v>
+        <v>515497</v>
       </c>
       <c r="R95" t="n">
-        <v>6924416</v>
+        <v>6924983</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11888,7 +11892,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120318823</v>
+        <v>120318837</v>
       </c>
       <c r="B96" t="n">
         <v>97930</v>
@@ -11923,7 +11927,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11932,10 +11936,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>515067</v>
+        <v>515326</v>
       </c>
       <c r="R96" t="n">
-        <v>6924720</v>
+        <v>6924467</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11994,7 +11998,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120318848</v>
+        <v>120318840</v>
       </c>
       <c r="B97" t="n">
         <v>97930</v>
@@ -12027,21 +12031,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>515521</v>
+        <v>514998</v>
       </c>
       <c r="R97" t="n">
-        <v>6924943</v>
+        <v>6924990</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12068,12 +12068,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12100,7 +12100,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120318818</v>
+        <v>120318844</v>
       </c>
       <c r="B98" t="n">
         <v>97930</v>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12144,10 +12144,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>514820</v>
+        <v>515557</v>
       </c>
       <c r="R98" t="n">
-        <v>6924711</v>
+        <v>6924620</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12206,7 +12206,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120318832</v>
+        <v>120318823</v>
       </c>
       <c r="B99" t="n">
         <v>97930</v>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12250,10 +12250,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>515203</v>
+        <v>515067</v>
       </c>
       <c r="R99" t="n">
-        <v>6924357</v>
+        <v>6924720</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12312,7 +12312,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120318815</v>
+        <v>120318832</v>
       </c>
       <c r="B100" t="n">
         <v>97930</v>
@@ -12347,7 +12347,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12356,10 +12356,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>514859</v>
+        <v>515203</v>
       </c>
       <c r="R100" t="n">
-        <v>6924782</v>
+        <v>6924357</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120318847</v>
+        <v>120318842</v>
       </c>
       <c r="B101" t="n">
         <v>97930</v>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12462,10 +12462,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>515636</v>
+        <v>515405</v>
       </c>
       <c r="R101" t="n">
-        <v>6924856</v>
+        <v>6924637</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12524,7 +12524,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120318852</v>
+        <v>120318827</v>
       </c>
       <c r="B102" t="n">
         <v>97930</v>
@@ -12557,17 +12557,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>515293</v>
+        <v>515136</v>
       </c>
       <c r="R102" t="n">
-        <v>6925084</v>
+        <v>6924416</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12594,12 +12598,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12626,7 +12630,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120318820</v>
+        <v>120318822</v>
       </c>
       <c r="B103" t="n">
         <v>97930</v>
@@ -12661,7 +12665,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12670,10 +12674,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>514913</v>
+        <v>515056</v>
       </c>
       <c r="R103" t="n">
-        <v>6924578</v>
+        <v>6924723</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12732,7 +12736,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120318833</v>
+        <v>120318824</v>
       </c>
       <c r="B104" t="n">
         <v>97930</v>
@@ -12767,7 +12771,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12776,10 +12780,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>515213</v>
+        <v>515085</v>
       </c>
       <c r="R104" t="n">
-        <v>6924361</v>
+        <v>6924717</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12838,7 +12842,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120318826</v>
+        <v>120318847</v>
       </c>
       <c r="B105" t="n">
         <v>97930</v>
@@ -12873,7 +12877,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12882,10 +12886,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>515119</v>
+        <v>515636</v>
       </c>
       <c r="R105" t="n">
-        <v>6924734</v>
+        <v>6924856</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12944,7 +12948,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120318828</v>
+        <v>120318812</v>
       </c>
       <c r="B106" t="n">
         <v>97930</v>
@@ -12979,7 +12983,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -12988,10 +12992,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>515127</v>
+        <v>515007</v>
       </c>
       <c r="R106" t="n">
-        <v>6924384</v>
+        <v>6924912</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13050,7 +13054,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120318824</v>
+        <v>120318829</v>
       </c>
       <c r="B107" t="n">
         <v>97930</v>
@@ -13085,7 +13089,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13094,10 +13098,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>515085</v>
+        <v>515142</v>
       </c>
       <c r="R107" t="n">
-        <v>6924717</v>
+        <v>6924327</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13156,7 +13160,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120318849</v>
+        <v>120318821</v>
       </c>
       <c r="B108" t="n">
         <v>97930</v>
@@ -13191,7 +13195,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -13200,10 +13204,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>515497</v>
+        <v>514957</v>
       </c>
       <c r="R108" t="n">
-        <v>6924983</v>
+        <v>6924623</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13262,7 +13266,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120318816</v>
+        <v>120318846</v>
       </c>
       <c r="B109" t="n">
         <v>97930</v>
@@ -13297,7 +13301,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -13306,10 +13310,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>514838</v>
+        <v>515647</v>
       </c>
       <c r="R109" t="n">
-        <v>6924796</v>
+        <v>6924817</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13368,7 +13372,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120318835</v>
+        <v>120318848</v>
       </c>
       <c r="B110" t="n">
         <v>97930</v>
@@ -13403,7 +13407,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13412,10 +13416,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>515229</v>
+        <v>515521</v>
       </c>
       <c r="R110" t="n">
-        <v>6924387</v>
+        <v>6924943</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13474,7 +13478,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120318819</v>
+        <v>120318834</v>
       </c>
       <c r="B111" t="n">
         <v>97930</v>
@@ -13509,7 +13513,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13518,10 +13522,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>514895</v>
+        <v>515221</v>
       </c>
       <c r="R111" t="n">
-        <v>6924584</v>
+        <v>6924386</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13580,7 +13584,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120318837</v>
+        <v>120318845</v>
       </c>
       <c r="B112" t="n">
         <v>97930</v>
@@ -13624,10 +13628,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>515326</v>
+        <v>515553</v>
       </c>
       <c r="R112" t="n">
-        <v>6924467</v>
+        <v>6924626</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13686,7 +13690,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120318813</v>
+        <v>120318826</v>
       </c>
       <c r="B113" t="n">
         <v>97930</v>
@@ -13721,7 +13725,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13730,10 +13734,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>514992</v>
+        <v>515119</v>
       </c>
       <c r="R113" t="n">
-        <v>6924909</v>
+        <v>6924734</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13792,7 +13796,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120318842</v>
+        <v>120318831</v>
       </c>
       <c r="B114" t="n">
         <v>97930</v>
@@ -13827,7 +13831,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13836,10 +13840,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>515405</v>
+        <v>515187</v>
       </c>
       <c r="R114" t="n">
-        <v>6924637</v>
+        <v>6924328</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13898,7 +13902,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120318846</v>
+        <v>120318852</v>
       </c>
       <c r="B115" t="n">
         <v>97930</v>
@@ -13931,21 +13935,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>515647</v>
+        <v>515293</v>
       </c>
       <c r="R115" t="n">
-        <v>6924817</v>
+        <v>6925084</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13972,12 +13972,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -9988,7 +9988,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120318833</v>
+        <v>120318823</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515213</v>
+        <v>515067</v>
       </c>
       <c r="R78" t="n">
-        <v>6924361</v>
+        <v>6924720</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120318843</v>
+        <v>120318837</v>
       </c>
       <c r="B79" t="n">
         <v>97930</v>
@@ -10127,17 +10127,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515289</v>
+        <v>515326</v>
       </c>
       <c r="R79" t="n">
-        <v>6924796</v>
+        <v>6924467</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10164,12 +10168,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10196,7 +10200,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120318817</v>
+        <v>120318824</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -10231,7 +10235,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -10240,10 +10244,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>514849</v>
+        <v>515085</v>
       </c>
       <c r="R80" t="n">
-        <v>6924760</v>
+        <v>6924717</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10408,7 +10412,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120318819</v>
+        <v>120318842</v>
       </c>
       <c r="B82" t="n">
         <v>97930</v>
@@ -10443,7 +10447,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10452,10 +10456,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>514895</v>
+        <v>515405</v>
       </c>
       <c r="R82" t="n">
-        <v>6924584</v>
+        <v>6924637</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10514,7 +10518,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120318841</v>
+        <v>120318827</v>
       </c>
       <c r="B83" t="n">
         <v>97930</v>
@@ -10549,7 +10553,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10558,10 +10562,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515403</v>
+        <v>515136</v>
       </c>
       <c r="R83" t="n">
-        <v>6924623</v>
+        <v>6924416</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10726,7 +10730,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120318830</v>
+        <v>120318812</v>
       </c>
       <c r="B85" t="n">
         <v>97930</v>
@@ -10761,7 +10765,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10770,10 +10774,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515149</v>
+        <v>515007</v>
       </c>
       <c r="R85" t="n">
-        <v>6924307</v>
+        <v>6924912</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10832,7 +10836,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120318835</v>
+        <v>120318852</v>
       </c>
       <c r="B86" t="n">
         <v>97930</v>
@@ -10865,21 +10869,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515229</v>
+        <v>515293</v>
       </c>
       <c r="R86" t="n">
-        <v>6924387</v>
+        <v>6925084</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10906,12 +10906,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10938,7 +10938,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120318818</v>
+        <v>120318849</v>
       </c>
       <c r="B87" t="n">
         <v>97930</v>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10982,10 +10982,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>514820</v>
+        <v>515497</v>
       </c>
       <c r="R87" t="n">
-        <v>6924711</v>
+        <v>6924983</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11044,7 +11044,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120318815</v>
+        <v>120318843</v>
       </c>
       <c r="B88" t="n">
         <v>97930</v>
@@ -11077,21 +11077,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>514859</v>
+        <v>515289</v>
       </c>
       <c r="R88" t="n">
-        <v>6924782</v>
+        <v>6924796</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11118,12 +11114,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11150,7 +11146,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120318820</v>
+        <v>120318819</v>
       </c>
       <c r="B89" t="n">
         <v>97930</v>
@@ -11185,7 +11181,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11194,10 +11190,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>514913</v>
+        <v>514895</v>
       </c>
       <c r="R89" t="n">
-        <v>6924578</v>
+        <v>6924584</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11256,7 +11252,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120318836</v>
+        <v>120318822</v>
       </c>
       <c r="B90" t="n">
         <v>97930</v>
@@ -11291,7 +11287,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11300,10 +11296,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>515223</v>
+        <v>515056</v>
       </c>
       <c r="R90" t="n">
-        <v>6924414</v>
+        <v>6924723</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11362,7 +11358,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120318814</v>
+        <v>120318832</v>
       </c>
       <c r="B91" t="n">
         <v>97930</v>
@@ -11397,7 +11393,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11406,10 +11402,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>514909</v>
+        <v>515203</v>
       </c>
       <c r="R91" t="n">
-        <v>6924793</v>
+        <v>6924357</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11468,7 +11464,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120318813</v>
+        <v>120318835</v>
       </c>
       <c r="B92" t="n">
         <v>97930</v>
@@ -11503,7 +11499,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11512,10 +11508,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>514992</v>
+        <v>515229</v>
       </c>
       <c r="R92" t="n">
-        <v>6924909</v>
+        <v>6924387</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11574,7 +11570,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120318816</v>
+        <v>120318818</v>
       </c>
       <c r="B93" t="n">
         <v>97930</v>
@@ -11609,7 +11605,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11618,10 +11614,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>514838</v>
+        <v>514820</v>
       </c>
       <c r="R93" t="n">
-        <v>6924796</v>
+        <v>6924711</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11680,7 +11676,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120318839</v>
+        <v>120318826</v>
       </c>
       <c r="B94" t="n">
         <v>97930</v>
@@ -11715,7 +11711,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11724,10 +11720,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>515335</v>
+        <v>515119</v>
       </c>
       <c r="R94" t="n">
-        <v>6924502</v>
+        <v>6924734</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11786,7 +11782,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120318849</v>
+        <v>120318834</v>
       </c>
       <c r="B95" t="n">
         <v>97930</v>
@@ -11821,7 +11817,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11830,10 +11826,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>515497</v>
+        <v>515221</v>
       </c>
       <c r="R95" t="n">
-        <v>6924983</v>
+        <v>6924386</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11892,7 +11888,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120318837</v>
+        <v>120318814</v>
       </c>
       <c r="B96" t="n">
         <v>97930</v>
@@ -11927,7 +11923,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>380</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11936,10 +11932,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>515326</v>
+        <v>514909</v>
       </c>
       <c r="R96" t="n">
-        <v>6924467</v>
+        <v>6924793</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11998,7 +11994,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120318840</v>
+        <v>120318839</v>
       </c>
       <c r="B97" t="n">
         <v>97930</v>
@@ -12031,17 +12027,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>514998</v>
+        <v>515335</v>
       </c>
       <c r="R97" t="n">
-        <v>6924990</v>
+        <v>6924502</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12068,12 +12068,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12100,7 +12100,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120318844</v>
+        <v>120318848</v>
       </c>
       <c r="B98" t="n">
         <v>97930</v>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12144,10 +12144,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>515557</v>
+        <v>515521</v>
       </c>
       <c r="R98" t="n">
-        <v>6924620</v>
+        <v>6924943</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12206,7 +12206,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120318823</v>
+        <v>120318829</v>
       </c>
       <c r="B99" t="n">
         <v>97930</v>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12250,10 +12250,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>515067</v>
+        <v>515142</v>
       </c>
       <c r="R99" t="n">
-        <v>6924720</v>
+        <v>6924327</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12312,7 +12312,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120318832</v>
+        <v>120318841</v>
       </c>
       <c r="B100" t="n">
         <v>97930</v>
@@ -12347,7 +12347,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12356,10 +12356,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>515203</v>
+        <v>515403</v>
       </c>
       <c r="R100" t="n">
-        <v>6924357</v>
+        <v>6924623</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120318842</v>
+        <v>120318817</v>
       </c>
       <c r="B101" t="n">
         <v>97930</v>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12462,10 +12462,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>515405</v>
+        <v>514849</v>
       </c>
       <c r="R101" t="n">
-        <v>6924637</v>
+        <v>6924760</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12524,7 +12524,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120318827</v>
+        <v>120318821</v>
       </c>
       <c r="B102" t="n">
         <v>97930</v>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -12568,10 +12568,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>515136</v>
+        <v>514957</v>
       </c>
       <c r="R102" t="n">
-        <v>6924416</v>
+        <v>6924623</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12630,7 +12630,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120318822</v>
+        <v>120318830</v>
       </c>
       <c r="B103" t="n">
         <v>97930</v>
@@ -12674,10 +12674,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>515056</v>
+        <v>515149</v>
       </c>
       <c r="R103" t="n">
-        <v>6924723</v>
+        <v>6924307</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120318824</v>
+        <v>120318846</v>
       </c>
       <c r="B104" t="n">
         <v>97930</v>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12780,10 +12780,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>515085</v>
+        <v>515647</v>
       </c>
       <c r="R104" t="n">
-        <v>6924717</v>
+        <v>6924817</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12948,7 +12948,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120318812</v>
+        <v>120318816</v>
       </c>
       <c r="B106" t="n">
         <v>97930</v>
@@ -12983,7 +12983,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -12992,10 +12992,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>515007</v>
+        <v>514838</v>
       </c>
       <c r="R106" t="n">
-        <v>6924912</v>
+        <v>6924796</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13054,7 +13054,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120318829</v>
+        <v>120318840</v>
       </c>
       <c r="B107" t="n">
         <v>97930</v>
@@ -13087,21 +13087,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>515142</v>
+        <v>514998</v>
       </c>
       <c r="R107" t="n">
-        <v>6924327</v>
+        <v>6924990</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13128,12 +13124,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13160,7 +13156,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120318821</v>
+        <v>120318845</v>
       </c>
       <c r="B108" t="n">
         <v>97930</v>
@@ -13195,7 +13191,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -13204,10 +13200,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>514957</v>
+        <v>515553</v>
       </c>
       <c r="R108" t="n">
-        <v>6924623</v>
+        <v>6924626</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13266,7 +13262,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120318846</v>
+        <v>120318844</v>
       </c>
       <c r="B109" t="n">
         <v>97930</v>
@@ -13301,7 +13297,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -13310,10 +13306,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>515647</v>
+        <v>515557</v>
       </c>
       <c r="R109" t="n">
-        <v>6924817</v>
+        <v>6924620</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13372,7 +13368,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120318848</v>
+        <v>120318813</v>
       </c>
       <c r="B110" t="n">
         <v>97930</v>
@@ -13407,7 +13403,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13416,10 +13412,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>515521</v>
+        <v>514992</v>
       </c>
       <c r="R110" t="n">
-        <v>6924943</v>
+        <v>6924909</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13478,7 +13474,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120318834</v>
+        <v>120318836</v>
       </c>
       <c r="B111" t="n">
         <v>97930</v>
@@ -13513,7 +13509,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13522,10 +13518,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>515221</v>
+        <v>515223</v>
       </c>
       <c r="R111" t="n">
-        <v>6924386</v>
+        <v>6924414</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13584,7 +13580,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120318845</v>
+        <v>120318833</v>
       </c>
       <c r="B112" t="n">
         <v>97930</v>
@@ -13619,7 +13615,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -13628,10 +13624,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>515553</v>
+        <v>515213</v>
       </c>
       <c r="R112" t="n">
-        <v>6924626</v>
+        <v>6924361</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13690,7 +13686,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120318826</v>
+        <v>120318831</v>
       </c>
       <c r="B113" t="n">
         <v>97930</v>
@@ -13725,7 +13721,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13734,10 +13730,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>515119</v>
+        <v>515187</v>
       </c>
       <c r="R113" t="n">
-        <v>6924734</v>
+        <v>6924328</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13796,7 +13792,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120318831</v>
+        <v>120318815</v>
       </c>
       <c r="B114" t="n">
         <v>97930</v>
@@ -13831,7 +13827,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13840,10 +13836,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>515187</v>
+        <v>514859</v>
       </c>
       <c r="R114" t="n">
-        <v>6924328</v>
+        <v>6924782</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13902,7 +13898,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120318852</v>
+        <v>120318820</v>
       </c>
       <c r="B115" t="n">
         <v>97930</v>
@@ -13935,17 +13931,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>515293</v>
+        <v>514913</v>
       </c>
       <c r="R115" t="n">
-        <v>6925084</v>
+        <v>6924578</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13972,12 +13972,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -9988,7 +9988,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120318823</v>
+        <v>120318846</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515067</v>
+        <v>515647</v>
       </c>
       <c r="R78" t="n">
-        <v>6924720</v>
+        <v>6924817</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120318837</v>
+        <v>120318822</v>
       </c>
       <c r="B79" t="n">
         <v>97930</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515326</v>
+        <v>515056</v>
       </c>
       <c r="R79" t="n">
-        <v>6924467</v>
+        <v>6924723</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10200,7 +10200,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120318824</v>
+        <v>120318839</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -10244,10 +10244,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515085</v>
+        <v>515335</v>
       </c>
       <c r="R80" t="n">
-        <v>6924717</v>
+        <v>6924502</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10306,7 +10306,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120318828</v>
+        <v>120318816</v>
       </c>
       <c r="B81" t="n">
         <v>97930</v>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10350,10 +10350,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515127</v>
+        <v>514838</v>
       </c>
       <c r="R81" t="n">
-        <v>6924384</v>
+        <v>6924796</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10412,7 +10412,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120318842</v>
+        <v>120318815</v>
       </c>
       <c r="B82" t="n">
         <v>97930</v>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10456,10 +10456,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515405</v>
+        <v>514859</v>
       </c>
       <c r="R82" t="n">
-        <v>6924637</v>
+        <v>6924782</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10518,7 +10518,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120318827</v>
+        <v>120318834</v>
       </c>
       <c r="B83" t="n">
         <v>97930</v>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10562,10 +10562,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515136</v>
+        <v>515221</v>
       </c>
       <c r="R83" t="n">
-        <v>6924416</v>
+        <v>6924386</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10624,7 +10624,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120318825</v>
+        <v>120318847</v>
       </c>
       <c r="B84" t="n">
         <v>97930</v>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10668,10 +10668,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515094</v>
+        <v>515636</v>
       </c>
       <c r="R84" t="n">
-        <v>6924722</v>
+        <v>6924856</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10730,7 +10730,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120318812</v>
+        <v>120318819</v>
       </c>
       <c r="B85" t="n">
         <v>97930</v>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10774,10 +10774,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515007</v>
+        <v>514895</v>
       </c>
       <c r="R85" t="n">
-        <v>6924912</v>
+        <v>6924584</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10836,7 +10836,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120318852</v>
+        <v>120318842</v>
       </c>
       <c r="B86" t="n">
         <v>97930</v>
@@ -10869,17 +10869,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515293</v>
+        <v>515405</v>
       </c>
       <c r="R86" t="n">
-        <v>6925084</v>
+        <v>6924637</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10906,12 +10910,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10938,7 +10942,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120318849</v>
+        <v>120318848</v>
       </c>
       <c r="B87" t="n">
         <v>97930</v>
@@ -10973,7 +10977,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10982,10 +10986,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515497</v>
+        <v>515521</v>
       </c>
       <c r="R87" t="n">
-        <v>6924983</v>
+        <v>6924943</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11044,7 +11048,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120318843</v>
+        <v>120318821</v>
       </c>
       <c r="B88" t="n">
         <v>97930</v>
@@ -11077,17 +11081,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>515289</v>
+        <v>514957</v>
       </c>
       <c r="R88" t="n">
-        <v>6924796</v>
+        <v>6924623</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11114,12 +11122,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11146,7 +11154,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120318819</v>
+        <v>120318814</v>
       </c>
       <c r="B89" t="n">
         <v>97930</v>
@@ -11181,7 +11189,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>380</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11190,10 +11198,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>514895</v>
+        <v>514909</v>
       </c>
       <c r="R89" t="n">
-        <v>6924584</v>
+        <v>6924793</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11252,7 +11260,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120318822</v>
+        <v>120318823</v>
       </c>
       <c r="B90" t="n">
         <v>97930</v>
@@ -11287,7 +11295,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11296,10 +11304,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>515056</v>
+        <v>515067</v>
       </c>
       <c r="R90" t="n">
-        <v>6924723</v>
+        <v>6924720</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11358,7 +11366,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120318832</v>
+        <v>120318817</v>
       </c>
       <c r="B91" t="n">
         <v>97930</v>
@@ -11393,7 +11401,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11402,10 +11410,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>515203</v>
+        <v>514849</v>
       </c>
       <c r="R91" t="n">
-        <v>6924357</v>
+        <v>6924760</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11464,7 +11472,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120318835</v>
+        <v>120318852</v>
       </c>
       <c r="B92" t="n">
         <v>97930</v>
@@ -11497,21 +11505,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>515229</v>
+        <v>515293</v>
       </c>
       <c r="R92" t="n">
-        <v>6924387</v>
+        <v>6925084</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11538,12 +11542,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11570,7 +11574,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120318818</v>
+        <v>120318831</v>
       </c>
       <c r="B93" t="n">
         <v>97930</v>
@@ -11605,7 +11609,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11614,10 +11618,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>514820</v>
+        <v>515187</v>
       </c>
       <c r="R93" t="n">
-        <v>6924711</v>
+        <v>6924328</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11676,7 +11680,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120318826</v>
+        <v>120318844</v>
       </c>
       <c r="B94" t="n">
         <v>97930</v>
@@ -11711,7 +11715,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11720,10 +11724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>515119</v>
+        <v>515557</v>
       </c>
       <c r="R94" t="n">
-        <v>6924734</v>
+        <v>6924620</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11782,7 +11786,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120318834</v>
+        <v>120318835</v>
       </c>
       <c r="B95" t="n">
         <v>97930</v>
@@ -11817,7 +11821,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11826,10 +11830,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>515221</v>
+        <v>515229</v>
       </c>
       <c r="R95" t="n">
-        <v>6924386</v>
+        <v>6924387</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11888,7 +11892,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120318814</v>
+        <v>120318849</v>
       </c>
       <c r="B96" t="n">
         <v>97930</v>
@@ -11923,7 +11927,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11932,10 +11936,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>514909</v>
+        <v>515497</v>
       </c>
       <c r="R96" t="n">
-        <v>6924793</v>
+        <v>6924983</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11994,7 +11998,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120318839</v>
+        <v>120318818</v>
       </c>
       <c r="B97" t="n">
         <v>97930</v>
@@ -12029,7 +12033,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12038,10 +12042,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>515335</v>
+        <v>514820</v>
       </c>
       <c r="R97" t="n">
-        <v>6924502</v>
+        <v>6924711</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12100,7 +12104,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120318848</v>
+        <v>120318820</v>
       </c>
       <c r="B98" t="n">
         <v>97930</v>
@@ -12135,7 +12139,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12144,10 +12148,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>515521</v>
+        <v>514913</v>
       </c>
       <c r="R98" t="n">
-        <v>6924943</v>
+        <v>6924578</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12206,7 +12210,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120318829</v>
+        <v>120318813</v>
       </c>
       <c r="B99" t="n">
         <v>97930</v>
@@ -12241,7 +12245,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12250,10 +12254,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>515142</v>
+        <v>514992</v>
       </c>
       <c r="R99" t="n">
-        <v>6924327</v>
+        <v>6924909</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12312,7 +12316,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120318841</v>
+        <v>120318832</v>
       </c>
       <c r="B100" t="n">
         <v>97930</v>
@@ -12347,7 +12351,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12356,10 +12360,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>515403</v>
+        <v>515203</v>
       </c>
       <c r="R100" t="n">
-        <v>6924623</v>
+        <v>6924357</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12418,7 +12422,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120318817</v>
+        <v>120318836</v>
       </c>
       <c r="B101" t="n">
         <v>97930</v>
@@ -12453,7 +12457,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12462,10 +12466,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>514849</v>
+        <v>515223</v>
       </c>
       <c r="R101" t="n">
-        <v>6924760</v>
+        <v>6924414</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12524,7 +12528,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120318821</v>
+        <v>120318828</v>
       </c>
       <c r="B102" t="n">
         <v>97930</v>
@@ -12559,7 +12563,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -12568,10 +12572,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>514957</v>
+        <v>515127</v>
       </c>
       <c r="R102" t="n">
-        <v>6924623</v>
+        <v>6924384</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12736,7 +12740,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120318846</v>
+        <v>120318829</v>
       </c>
       <c r="B104" t="n">
         <v>97930</v>
@@ -12771,7 +12775,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12780,10 +12784,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>515647</v>
+        <v>515142</v>
       </c>
       <c r="R104" t="n">
-        <v>6924817</v>
+        <v>6924327</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12842,7 +12846,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120318847</v>
+        <v>120318827</v>
       </c>
       <c r="B105" t="n">
         <v>97930</v>
@@ -12877,7 +12881,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12886,10 +12890,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>515636</v>
+        <v>515136</v>
       </c>
       <c r="R105" t="n">
-        <v>6924856</v>
+        <v>6924416</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12948,7 +12952,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120318816</v>
+        <v>120318841</v>
       </c>
       <c r="B106" t="n">
         <v>97930</v>
@@ -12983,7 +12987,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -12992,10 +12996,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>514838</v>
+        <v>515403</v>
       </c>
       <c r="R106" t="n">
-        <v>6924796</v>
+        <v>6924623</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13054,7 +13058,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120318840</v>
+        <v>120318824</v>
       </c>
       <c r="B107" t="n">
         <v>97930</v>
@@ -13087,17 +13091,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>514998</v>
+        <v>515085</v>
       </c>
       <c r="R107" t="n">
-        <v>6924990</v>
+        <v>6924717</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13124,12 +13132,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13156,7 +13164,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120318845</v>
+        <v>120318826</v>
       </c>
       <c r="B108" t="n">
         <v>97930</v>
@@ -13200,10 +13208,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>515553</v>
+        <v>515119</v>
       </c>
       <c r="R108" t="n">
-        <v>6924626</v>
+        <v>6924734</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13262,7 +13270,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120318844</v>
+        <v>120318843</v>
       </c>
       <c r="B109" t="n">
         <v>97930</v>
@@ -13295,21 +13303,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>515557</v>
+        <v>515289</v>
       </c>
       <c r="R109" t="n">
-        <v>6924620</v>
+        <v>6924796</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13336,12 +13340,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13368,7 +13372,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120318813</v>
+        <v>120318845</v>
       </c>
       <c r="B110" t="n">
         <v>97930</v>
@@ -13403,7 +13407,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13412,10 +13416,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>514992</v>
+        <v>515553</v>
       </c>
       <c r="R110" t="n">
-        <v>6924909</v>
+        <v>6924626</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13474,7 +13478,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120318836</v>
+        <v>120318825</v>
       </c>
       <c r="B111" t="n">
         <v>97930</v>
@@ -13509,7 +13513,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13518,10 +13522,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>515223</v>
+        <v>515094</v>
       </c>
       <c r="R111" t="n">
-        <v>6924414</v>
+        <v>6924722</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13580,7 +13584,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120318833</v>
+        <v>120318840</v>
       </c>
       <c r="B112" t="n">
         <v>97930</v>
@@ -13613,21 +13617,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>515213</v>
+        <v>514998</v>
       </c>
       <c r="R112" t="n">
-        <v>6924361</v>
+        <v>6924990</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13654,12 +13654,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13686,7 +13686,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120318831</v>
+        <v>120318833</v>
       </c>
       <c r="B113" t="n">
         <v>97930</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13730,10 +13730,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>515187</v>
+        <v>515213</v>
       </c>
       <c r="R113" t="n">
-        <v>6924328</v>
+        <v>6924361</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13792,7 +13792,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120318815</v>
+        <v>120318812</v>
       </c>
       <c r="B114" t="n">
         <v>97930</v>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13836,10 +13836,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>514859</v>
+        <v>515007</v>
       </c>
       <c r="R114" t="n">
-        <v>6924782</v>
+        <v>6924912</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13898,7 +13898,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120318820</v>
+        <v>120318837</v>
       </c>
       <c r="B115" t="n">
         <v>97930</v>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>514913</v>
+        <v>515326</v>
       </c>
       <c r="R115" t="n">
-        <v>6924578</v>
+        <v>6924467</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -9988,7 +9988,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120318846</v>
+        <v>120318839</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515647</v>
+        <v>515335</v>
       </c>
       <c r="R78" t="n">
-        <v>6924817</v>
+        <v>6924502</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120318822</v>
+        <v>120318834</v>
       </c>
       <c r="B79" t="n">
         <v>97930</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515056</v>
+        <v>515221</v>
       </c>
       <c r="R79" t="n">
-        <v>6924723</v>
+        <v>6924386</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10200,7 +10200,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120318839</v>
+        <v>120318813</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -10244,10 +10244,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515335</v>
+        <v>514992</v>
       </c>
       <c r="R80" t="n">
-        <v>6924502</v>
+        <v>6924909</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10306,7 +10306,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120318816</v>
+        <v>120318837</v>
       </c>
       <c r="B81" t="n">
         <v>97930</v>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10350,10 +10350,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>514838</v>
+        <v>515326</v>
       </c>
       <c r="R81" t="n">
-        <v>6924796</v>
+        <v>6924467</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10412,7 +10412,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120318815</v>
+        <v>120318828</v>
       </c>
       <c r="B82" t="n">
         <v>97930</v>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10456,10 +10456,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>514859</v>
+        <v>515127</v>
       </c>
       <c r="R82" t="n">
-        <v>6924782</v>
+        <v>6924384</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10518,7 +10518,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120318834</v>
+        <v>120318832</v>
       </c>
       <c r="B83" t="n">
         <v>97930</v>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10562,10 +10562,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515221</v>
+        <v>515203</v>
       </c>
       <c r="R83" t="n">
-        <v>6924386</v>
+        <v>6924357</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10624,7 +10624,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120318847</v>
+        <v>120318821</v>
       </c>
       <c r="B84" t="n">
         <v>97930</v>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10668,10 +10668,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515636</v>
+        <v>514957</v>
       </c>
       <c r="R84" t="n">
-        <v>6924856</v>
+        <v>6924623</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10730,7 +10730,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120318819</v>
+        <v>120318830</v>
       </c>
       <c r="B85" t="n">
         <v>97930</v>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10774,10 +10774,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>514895</v>
+        <v>515149</v>
       </c>
       <c r="R85" t="n">
-        <v>6924584</v>
+        <v>6924307</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10836,7 +10836,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120318842</v>
+        <v>120318848</v>
       </c>
       <c r="B86" t="n">
         <v>97930</v>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10880,10 +10880,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515405</v>
+        <v>515521</v>
       </c>
       <c r="R86" t="n">
-        <v>6924637</v>
+        <v>6924943</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10942,7 +10942,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120318848</v>
+        <v>120318825</v>
       </c>
       <c r="B87" t="n">
         <v>97930</v>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515521</v>
+        <v>515094</v>
       </c>
       <c r="R87" t="n">
-        <v>6924943</v>
+        <v>6924722</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11048,7 +11048,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120318821</v>
+        <v>120318833</v>
       </c>
       <c r="B88" t="n">
         <v>97930</v>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11092,10 +11092,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>514957</v>
+        <v>515213</v>
       </c>
       <c r="R88" t="n">
-        <v>6924623</v>
+        <v>6924361</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120318814</v>
+        <v>120318836</v>
       </c>
       <c r="B89" t="n">
         <v>97930</v>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11198,10 +11198,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>514909</v>
+        <v>515223</v>
       </c>
       <c r="R89" t="n">
-        <v>6924793</v>
+        <v>6924414</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11260,7 +11260,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120318823</v>
+        <v>120318818</v>
       </c>
       <c r="B90" t="n">
         <v>97930</v>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11304,10 +11304,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>515067</v>
+        <v>514820</v>
       </c>
       <c r="R90" t="n">
-        <v>6924720</v>
+        <v>6924711</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11366,7 +11366,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120318817</v>
+        <v>120318845</v>
       </c>
       <c r="B91" t="n">
         <v>97930</v>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11410,10 +11410,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>514849</v>
+        <v>515553</v>
       </c>
       <c r="R91" t="n">
-        <v>6924760</v>
+        <v>6924626</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11472,7 +11472,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120318852</v>
+        <v>120318812</v>
       </c>
       <c r="B92" t="n">
         <v>97930</v>
@@ -11505,17 +11505,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>515293</v>
+        <v>515007</v>
       </c>
       <c r="R92" t="n">
-        <v>6925084</v>
+        <v>6924912</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11542,12 +11546,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11574,7 +11578,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120318831</v>
+        <v>120318849</v>
       </c>
       <c r="B93" t="n">
         <v>97930</v>
@@ -11609,7 +11613,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11618,10 +11622,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>515187</v>
+        <v>515497</v>
       </c>
       <c r="R93" t="n">
-        <v>6924328</v>
+        <v>6924983</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11680,7 +11684,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120318844</v>
+        <v>120318819</v>
       </c>
       <c r="B94" t="n">
         <v>97930</v>
@@ -11715,7 +11719,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11724,10 +11728,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>515557</v>
+        <v>514895</v>
       </c>
       <c r="R94" t="n">
-        <v>6924620</v>
+        <v>6924584</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11786,7 +11790,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120318835</v>
+        <v>120318842</v>
       </c>
       <c r="B95" t="n">
         <v>97930</v>
@@ -11821,7 +11825,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11830,10 +11834,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>515229</v>
+        <v>515405</v>
       </c>
       <c r="R95" t="n">
-        <v>6924387</v>
+        <v>6924637</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11892,7 +11896,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120318849</v>
+        <v>120318817</v>
       </c>
       <c r="B96" t="n">
         <v>97930</v>
@@ -11927,7 +11931,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11936,10 +11940,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>515497</v>
+        <v>514849</v>
       </c>
       <c r="R96" t="n">
-        <v>6924983</v>
+        <v>6924760</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11998,7 +12002,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120318818</v>
+        <v>120318829</v>
       </c>
       <c r="B97" t="n">
         <v>97930</v>
@@ -12033,7 +12037,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12042,10 +12046,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>514820</v>
+        <v>515142</v>
       </c>
       <c r="R97" t="n">
-        <v>6924711</v>
+        <v>6924327</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12104,7 +12108,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120318820</v>
+        <v>120318824</v>
       </c>
       <c r="B98" t="n">
         <v>97930</v>
@@ -12139,7 +12143,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12148,10 +12152,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>514913</v>
+        <v>515085</v>
       </c>
       <c r="R98" t="n">
-        <v>6924578</v>
+        <v>6924717</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12210,7 +12214,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120318813</v>
+        <v>120318822</v>
       </c>
       <c r="B99" t="n">
         <v>97930</v>
@@ -12245,7 +12249,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12254,10 +12258,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>514992</v>
+        <v>515056</v>
       </c>
       <c r="R99" t="n">
-        <v>6924909</v>
+        <v>6924723</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12316,7 +12320,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120318832</v>
+        <v>120318816</v>
       </c>
       <c r="B100" t="n">
         <v>97930</v>
@@ -12351,7 +12355,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12360,10 +12364,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>515203</v>
+        <v>514838</v>
       </c>
       <c r="R100" t="n">
-        <v>6924357</v>
+        <v>6924796</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12422,7 +12426,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120318836</v>
+        <v>120318826</v>
       </c>
       <c r="B101" t="n">
         <v>97930</v>
@@ -12457,7 +12461,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12466,10 +12470,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>515223</v>
+        <v>515119</v>
       </c>
       <c r="R101" t="n">
-        <v>6924414</v>
+        <v>6924734</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12528,7 +12532,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120318828</v>
+        <v>120318814</v>
       </c>
       <c r="B102" t="n">
         <v>97930</v>
@@ -12563,7 +12567,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>380</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -12572,10 +12576,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>515127</v>
+        <v>514909</v>
       </c>
       <c r="R102" t="n">
-        <v>6924384</v>
+        <v>6924793</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12634,7 +12638,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120318830</v>
+        <v>120318831</v>
       </c>
       <c r="B103" t="n">
         <v>97930</v>
@@ -12669,7 +12673,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12678,10 +12682,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>515149</v>
+        <v>515187</v>
       </c>
       <c r="R103" t="n">
-        <v>6924307</v>
+        <v>6924328</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12740,7 +12744,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120318829</v>
+        <v>120318815</v>
       </c>
       <c r="B104" t="n">
         <v>97930</v>
@@ -12775,7 +12779,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12784,10 +12788,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>515142</v>
+        <v>514859</v>
       </c>
       <c r="R104" t="n">
-        <v>6924327</v>
+        <v>6924782</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12846,7 +12850,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120318827</v>
+        <v>120318820</v>
       </c>
       <c r="B105" t="n">
         <v>97930</v>
@@ -12881,7 +12885,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12890,10 +12894,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>515136</v>
+        <v>514913</v>
       </c>
       <c r="R105" t="n">
-        <v>6924416</v>
+        <v>6924578</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12952,7 +12956,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120318841</v>
+        <v>120318843</v>
       </c>
       <c r="B106" t="n">
         <v>97930</v>
@@ -12985,21 +12989,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>515403</v>
+        <v>515289</v>
       </c>
       <c r="R106" t="n">
-        <v>6924623</v>
+        <v>6924796</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13058,7 +13058,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120318824</v>
+        <v>120318841</v>
       </c>
       <c r="B107" t="n">
         <v>97930</v>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>515085</v>
+        <v>515403</v>
       </c>
       <c r="R107" t="n">
-        <v>6924717</v>
+        <v>6924623</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13164,7 +13164,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120318826</v>
+        <v>120318835</v>
       </c>
       <c r="B108" t="n">
         <v>97930</v>
@@ -13199,7 +13199,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -13208,10 +13208,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>515119</v>
+        <v>515229</v>
       </c>
       <c r="R108" t="n">
-        <v>6924734</v>
+        <v>6924387</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13270,7 +13270,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120318843</v>
+        <v>120318847</v>
       </c>
       <c r="B109" t="n">
         <v>97930</v>
@@ -13303,17 +13303,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>515289</v>
+        <v>515636</v>
       </c>
       <c r="R109" t="n">
-        <v>6924796</v>
+        <v>6924856</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13340,12 +13344,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13372,7 +13376,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120318845</v>
+        <v>120318827</v>
       </c>
       <c r="B110" t="n">
         <v>97930</v>
@@ -13407,7 +13411,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13416,10 +13420,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>515553</v>
+        <v>515136</v>
       </c>
       <c r="R110" t="n">
-        <v>6924626</v>
+        <v>6924416</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13478,7 +13482,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120318825</v>
+        <v>120318844</v>
       </c>
       <c r="B111" t="n">
         <v>97930</v>
@@ -13513,7 +13517,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13522,10 +13526,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>515094</v>
+        <v>515557</v>
       </c>
       <c r="R111" t="n">
-        <v>6924722</v>
+        <v>6924620</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13686,7 +13690,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120318833</v>
+        <v>120318823</v>
       </c>
       <c r="B113" t="n">
         <v>97930</v>
@@ -13721,7 +13725,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13730,10 +13734,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>515213</v>
+        <v>515067</v>
       </c>
       <c r="R113" t="n">
-        <v>6924361</v>
+        <v>6924720</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13792,7 +13796,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120318812</v>
+        <v>120318846</v>
       </c>
       <c r="B114" t="n">
         <v>97930</v>
@@ -13827,7 +13831,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13836,10 +13840,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>515007</v>
+        <v>515647</v>
       </c>
       <c r="R114" t="n">
-        <v>6924912</v>
+        <v>6924817</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13898,7 +13902,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120318837</v>
+        <v>120318852</v>
       </c>
       <c r="B115" t="n">
         <v>97930</v>
@@ -13931,21 +13935,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>515326</v>
+        <v>515293</v>
       </c>
       <c r="R115" t="n">
-        <v>6924467</v>
+        <v>6925084</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13972,12 +13972,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -9988,7 +9988,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120318839</v>
+        <v>120318830</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515335</v>
+        <v>515149</v>
       </c>
       <c r="R78" t="n">
-        <v>6924502</v>
+        <v>6924307</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120318834</v>
+        <v>120318837</v>
       </c>
       <c r="B79" t="n">
         <v>97930</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515221</v>
+        <v>515326</v>
       </c>
       <c r="R79" t="n">
-        <v>6924386</v>
+        <v>6924467</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10200,7 +10200,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120318813</v>
+        <v>120318824</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -10244,10 +10244,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>514992</v>
+        <v>515085</v>
       </c>
       <c r="R80" t="n">
-        <v>6924909</v>
+        <v>6924717</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10306,7 +10306,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120318837</v>
+        <v>120318840</v>
       </c>
       <c r="B81" t="n">
         <v>97930</v>
@@ -10339,21 +10339,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515326</v>
+        <v>514998</v>
       </c>
       <c r="R81" t="n">
-        <v>6924467</v>
+        <v>6924990</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10380,12 +10376,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10412,7 +10408,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120318828</v>
+        <v>120318821</v>
       </c>
       <c r="B82" t="n">
         <v>97930</v>
@@ -10447,7 +10443,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10456,10 +10452,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515127</v>
+        <v>514957</v>
       </c>
       <c r="R82" t="n">
-        <v>6924384</v>
+        <v>6924623</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10518,7 +10514,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120318832</v>
+        <v>120318849</v>
       </c>
       <c r="B83" t="n">
         <v>97930</v>
@@ -10553,7 +10549,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10562,10 +10558,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515203</v>
+        <v>515497</v>
       </c>
       <c r="R83" t="n">
-        <v>6924357</v>
+        <v>6924983</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10624,7 +10620,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120318821</v>
+        <v>120318829</v>
       </c>
       <c r="B84" t="n">
         <v>97930</v>
@@ -10659,7 +10655,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10668,10 +10664,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>514957</v>
+        <v>515142</v>
       </c>
       <c r="R84" t="n">
-        <v>6924623</v>
+        <v>6924327</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10730,7 +10726,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120318830</v>
+        <v>120318841</v>
       </c>
       <c r="B85" t="n">
         <v>97930</v>
@@ -10765,7 +10761,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10774,10 +10770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515149</v>
+        <v>515403</v>
       </c>
       <c r="R85" t="n">
-        <v>6924307</v>
+        <v>6924623</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10836,7 +10832,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120318848</v>
+        <v>120318812</v>
       </c>
       <c r="B86" t="n">
         <v>97930</v>
@@ -10871,7 +10867,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10880,10 +10876,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515521</v>
+        <v>515007</v>
       </c>
       <c r="R86" t="n">
-        <v>6924943</v>
+        <v>6924912</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10942,7 +10938,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120318825</v>
+        <v>120318831</v>
       </c>
       <c r="B87" t="n">
         <v>97930</v>
@@ -10977,7 +10973,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10986,10 +10982,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515094</v>
+        <v>515187</v>
       </c>
       <c r="R87" t="n">
-        <v>6924722</v>
+        <v>6924328</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11048,7 +11044,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120318833</v>
+        <v>120318813</v>
       </c>
       <c r="B88" t="n">
         <v>97930</v>
@@ -11083,7 +11079,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11092,10 +11088,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>515213</v>
+        <v>514992</v>
       </c>
       <c r="R88" t="n">
-        <v>6924361</v>
+        <v>6924909</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11154,7 +11150,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120318836</v>
+        <v>120318847</v>
       </c>
       <c r="B89" t="n">
         <v>97930</v>
@@ -11189,7 +11185,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11198,10 +11194,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>515223</v>
+        <v>515636</v>
       </c>
       <c r="R89" t="n">
-        <v>6924414</v>
+        <v>6924856</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11260,7 +11256,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120318818</v>
+        <v>120318827</v>
       </c>
       <c r="B90" t="n">
         <v>97930</v>
@@ -11295,7 +11291,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11304,10 +11300,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>514820</v>
+        <v>515136</v>
       </c>
       <c r="R90" t="n">
-        <v>6924711</v>
+        <v>6924416</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11366,7 +11362,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120318845</v>
+        <v>120318835</v>
       </c>
       <c r="B91" t="n">
         <v>97930</v>
@@ -11401,7 +11397,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11410,10 +11406,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>515553</v>
+        <v>515229</v>
       </c>
       <c r="R91" t="n">
-        <v>6924626</v>
+        <v>6924387</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11472,7 +11468,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120318812</v>
+        <v>120318839</v>
       </c>
       <c r="B92" t="n">
         <v>97930</v>
@@ -11507,7 +11503,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11516,10 +11512,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>515007</v>
+        <v>515335</v>
       </c>
       <c r="R92" t="n">
-        <v>6924912</v>
+        <v>6924502</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11578,7 +11574,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120318849</v>
+        <v>120318843</v>
       </c>
       <c r="B93" t="n">
         <v>97930</v>
@@ -11611,21 +11607,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>515497</v>
+        <v>515289</v>
       </c>
       <c r="R93" t="n">
-        <v>6924983</v>
+        <v>6924796</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11652,12 +11644,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11684,7 +11676,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120318819</v>
+        <v>120318823</v>
       </c>
       <c r="B94" t="n">
         <v>97930</v>
@@ -11719,7 +11711,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11728,10 +11720,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>514895</v>
+        <v>515067</v>
       </c>
       <c r="R94" t="n">
-        <v>6924584</v>
+        <v>6924720</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11790,7 +11782,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120318842</v>
+        <v>120318833</v>
       </c>
       <c r="B95" t="n">
         <v>97930</v>
@@ -11825,7 +11817,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11834,10 +11826,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>515405</v>
+        <v>515213</v>
       </c>
       <c r="R95" t="n">
-        <v>6924637</v>
+        <v>6924361</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11896,7 +11888,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120318817</v>
+        <v>120318820</v>
       </c>
       <c r="B96" t="n">
         <v>97930</v>
@@ -11931,7 +11923,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11940,10 +11932,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>514849</v>
+        <v>514913</v>
       </c>
       <c r="R96" t="n">
-        <v>6924760</v>
+        <v>6924578</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12002,7 +11994,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120318829</v>
+        <v>120318836</v>
       </c>
       <c r="B97" t="n">
         <v>97930</v>
@@ -12037,7 +12029,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12046,10 +12038,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>515142</v>
+        <v>515223</v>
       </c>
       <c r="R97" t="n">
-        <v>6924327</v>
+        <v>6924414</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12108,7 +12100,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120318824</v>
+        <v>120318845</v>
       </c>
       <c r="B98" t="n">
         <v>97930</v>
@@ -12143,7 +12135,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12152,10 +12144,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>515085</v>
+        <v>515553</v>
       </c>
       <c r="R98" t="n">
-        <v>6924717</v>
+        <v>6924626</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12214,7 +12206,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120318822</v>
+        <v>120318818</v>
       </c>
       <c r="B99" t="n">
         <v>97930</v>
@@ -12249,7 +12241,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12258,10 +12250,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>515056</v>
+        <v>514820</v>
       </c>
       <c r="R99" t="n">
-        <v>6924723</v>
+        <v>6924711</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12320,7 +12312,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120318816</v>
+        <v>120318817</v>
       </c>
       <c r="B100" t="n">
         <v>97930</v>
@@ -12355,7 +12347,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12364,10 +12356,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>514838</v>
+        <v>514849</v>
       </c>
       <c r="R100" t="n">
-        <v>6924796</v>
+        <v>6924760</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12426,7 +12418,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120318826</v>
+        <v>120318846</v>
       </c>
       <c r="B101" t="n">
         <v>97930</v>
@@ -12461,7 +12453,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12470,10 +12462,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>515119</v>
+        <v>515647</v>
       </c>
       <c r="R101" t="n">
-        <v>6924734</v>
+        <v>6924817</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12532,7 +12524,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120318814</v>
+        <v>120318816</v>
       </c>
       <c r="B102" t="n">
         <v>97930</v>
@@ -12567,7 +12559,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -12576,10 +12568,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>514909</v>
+        <v>514838</v>
       </c>
       <c r="R102" t="n">
-        <v>6924793</v>
+        <v>6924796</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12638,7 +12630,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120318831</v>
+        <v>120318842</v>
       </c>
       <c r="B103" t="n">
         <v>97930</v>
@@ -12673,7 +12665,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12682,10 +12674,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>515187</v>
+        <v>515405</v>
       </c>
       <c r="R103" t="n">
-        <v>6924328</v>
+        <v>6924637</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12744,7 +12736,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120318815</v>
+        <v>120318819</v>
       </c>
       <c r="B104" t="n">
         <v>97930</v>
@@ -12788,10 +12780,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>514859</v>
+        <v>514895</v>
       </c>
       <c r="R104" t="n">
-        <v>6924782</v>
+        <v>6924584</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12850,7 +12842,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120318820</v>
+        <v>120318834</v>
       </c>
       <c r="B105" t="n">
         <v>97930</v>
@@ -12885,7 +12877,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12894,10 +12886,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>514913</v>
+        <v>515221</v>
       </c>
       <c r="R105" t="n">
-        <v>6924578</v>
+        <v>6924386</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12956,7 +12948,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120318843</v>
+        <v>120318828</v>
       </c>
       <c r="B106" t="n">
         <v>97930</v>
@@ -12989,17 +12981,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>515289</v>
+        <v>515127</v>
       </c>
       <c r="R106" t="n">
-        <v>6924796</v>
+        <v>6924384</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13026,12 +13022,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13058,7 +13054,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120318841</v>
+        <v>120318825</v>
       </c>
       <c r="B107" t="n">
         <v>97930</v>
@@ -13093,7 +13089,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13102,10 +13098,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>515403</v>
+        <v>515094</v>
       </c>
       <c r="R107" t="n">
-        <v>6924623</v>
+        <v>6924722</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13164,7 +13160,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120318835</v>
+        <v>120318832</v>
       </c>
       <c r="B108" t="n">
         <v>97930</v>
@@ -13199,7 +13195,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -13208,10 +13204,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>515229</v>
+        <v>515203</v>
       </c>
       <c r="R108" t="n">
-        <v>6924387</v>
+        <v>6924357</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13270,7 +13266,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120318847</v>
+        <v>120318815</v>
       </c>
       <c r="B109" t="n">
         <v>97930</v>
@@ -13305,7 +13301,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -13314,10 +13310,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>515636</v>
+        <v>514859</v>
       </c>
       <c r="R109" t="n">
-        <v>6924856</v>
+        <v>6924782</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13376,7 +13372,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120318827</v>
+        <v>120318822</v>
       </c>
       <c r="B110" t="n">
         <v>97930</v>
@@ -13411,7 +13407,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13420,10 +13416,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>515136</v>
+        <v>515056</v>
       </c>
       <c r="R110" t="n">
-        <v>6924416</v>
+        <v>6924723</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13588,7 +13584,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120318840</v>
+        <v>120318814</v>
       </c>
       <c r="B112" t="n">
         <v>97930</v>
@@ -13621,17 +13617,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>514998</v>
+        <v>514909</v>
       </c>
       <c r="R112" t="n">
-        <v>6924990</v>
+        <v>6924793</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13658,12 +13658,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13690,7 +13690,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120318823</v>
+        <v>120318826</v>
       </c>
       <c r="B113" t="n">
         <v>97930</v>
@@ -13725,7 +13725,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13734,10 +13734,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>515067</v>
+        <v>515119</v>
       </c>
       <c r="R113" t="n">
-        <v>6924720</v>
+        <v>6924734</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13796,7 +13796,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120318846</v>
+        <v>120318848</v>
       </c>
       <c r="B114" t="n">
         <v>97930</v>
@@ -13831,7 +13831,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>515647</v>
+        <v>515521</v>
       </c>
       <c r="R114" t="n">
-        <v>6924817</v>
+        <v>6924943</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -9988,7 +9988,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120318830</v>
+        <v>120318816</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515149</v>
+        <v>514838</v>
       </c>
       <c r="R78" t="n">
-        <v>6924307</v>
+        <v>6924796</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120318837</v>
+        <v>120318817</v>
       </c>
       <c r="B79" t="n">
         <v>97930</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515326</v>
+        <v>514849</v>
       </c>
       <c r="R79" t="n">
-        <v>6924467</v>
+        <v>6924760</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10200,7 +10200,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120318824</v>
+        <v>120318832</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -10244,10 +10244,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515085</v>
+        <v>515203</v>
       </c>
       <c r="R80" t="n">
-        <v>6924717</v>
+        <v>6924357</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10306,7 +10306,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120318840</v>
+        <v>120318824</v>
       </c>
       <c r="B81" t="n">
         <v>97930</v>
@@ -10339,17 +10339,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>514998</v>
+        <v>515085</v>
       </c>
       <c r="R81" t="n">
-        <v>6924990</v>
+        <v>6924717</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10376,12 +10380,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10408,7 +10412,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120318821</v>
+        <v>120318815</v>
       </c>
       <c r="B82" t="n">
         <v>97930</v>
@@ -10443,7 +10447,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10452,10 +10456,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>514957</v>
+        <v>514859</v>
       </c>
       <c r="R82" t="n">
-        <v>6924623</v>
+        <v>6924782</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10514,7 +10518,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120318849</v>
+        <v>120318827</v>
       </c>
       <c r="B83" t="n">
         <v>97930</v>
@@ -10549,7 +10553,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10558,10 +10562,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515497</v>
+        <v>515136</v>
       </c>
       <c r="R83" t="n">
-        <v>6924983</v>
+        <v>6924416</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10620,7 +10624,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120318829</v>
+        <v>120318823</v>
       </c>
       <c r="B84" t="n">
         <v>97930</v>
@@ -10655,7 +10659,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10664,10 +10668,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515142</v>
+        <v>515067</v>
       </c>
       <c r="R84" t="n">
-        <v>6924327</v>
+        <v>6924720</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10726,7 +10730,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120318841</v>
+        <v>120318846</v>
       </c>
       <c r="B85" t="n">
         <v>97930</v>
@@ -10761,7 +10765,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10770,10 +10774,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515403</v>
+        <v>515647</v>
       </c>
       <c r="R85" t="n">
-        <v>6924623</v>
+        <v>6924817</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10832,7 +10836,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120318812</v>
+        <v>120318833</v>
       </c>
       <c r="B86" t="n">
         <v>97930</v>
@@ -10867,7 +10871,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10876,10 +10880,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515007</v>
+        <v>515213</v>
       </c>
       <c r="R86" t="n">
-        <v>6924912</v>
+        <v>6924361</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10938,7 +10942,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120318831</v>
+        <v>120318836</v>
       </c>
       <c r="B87" t="n">
         <v>97930</v>
@@ -10973,7 +10977,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10982,10 +10986,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515187</v>
+        <v>515223</v>
       </c>
       <c r="R87" t="n">
-        <v>6924328</v>
+        <v>6924414</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11044,7 +11048,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120318813</v>
+        <v>120318822</v>
       </c>
       <c r="B88" t="n">
         <v>97930</v>
@@ -11079,7 +11083,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11088,10 +11092,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>514992</v>
+        <v>515056</v>
       </c>
       <c r="R88" t="n">
-        <v>6924909</v>
+        <v>6924723</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11150,7 +11154,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120318847</v>
+        <v>120318825</v>
       </c>
       <c r="B89" t="n">
         <v>97930</v>
@@ -11185,7 +11189,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11194,10 +11198,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>515636</v>
+        <v>515094</v>
       </c>
       <c r="R89" t="n">
-        <v>6924856</v>
+        <v>6924722</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11256,7 +11260,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120318827</v>
+        <v>120318848</v>
       </c>
       <c r="B90" t="n">
         <v>97930</v>
@@ -11291,7 +11295,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11300,10 +11304,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>515136</v>
+        <v>515521</v>
       </c>
       <c r="R90" t="n">
-        <v>6924416</v>
+        <v>6924943</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11362,7 +11366,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120318835</v>
+        <v>120318843</v>
       </c>
       <c r="B91" t="n">
         <v>97930</v>
@@ -11395,21 +11399,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>515229</v>
+        <v>515289</v>
       </c>
       <c r="R91" t="n">
-        <v>6924387</v>
+        <v>6924796</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11436,12 +11436,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11468,7 +11468,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120318839</v>
+        <v>120318835</v>
       </c>
       <c r="B92" t="n">
         <v>97930</v>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>515335</v>
+        <v>515229</v>
       </c>
       <c r="R92" t="n">
-        <v>6924502</v>
+        <v>6924387</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120318843</v>
+        <v>120318840</v>
       </c>
       <c r="B93" t="n">
         <v>97930</v>
@@ -11614,10 +11614,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>515289</v>
+        <v>514998</v>
       </c>
       <c r="R93" t="n">
-        <v>6924796</v>
+        <v>6924990</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11676,7 +11676,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120318823</v>
+        <v>120318828</v>
       </c>
       <c r="B94" t="n">
         <v>97930</v>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11720,10 +11720,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>515067</v>
+        <v>515127</v>
       </c>
       <c r="R94" t="n">
-        <v>6924720</v>
+        <v>6924384</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11782,7 +11782,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120318833</v>
+        <v>120318839</v>
       </c>
       <c r="B95" t="n">
         <v>97930</v>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11826,10 +11826,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>515213</v>
+        <v>515335</v>
       </c>
       <c r="R95" t="n">
-        <v>6924361</v>
+        <v>6924502</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11888,7 +11888,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120318820</v>
+        <v>120318829</v>
       </c>
       <c r="B96" t="n">
         <v>97930</v>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11932,10 +11932,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>514913</v>
+        <v>515142</v>
       </c>
       <c r="R96" t="n">
-        <v>6924578</v>
+        <v>6924327</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120318836</v>
+        <v>120318834</v>
       </c>
       <c r="B97" t="n">
         <v>97930</v>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12038,10 +12038,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>515223</v>
+        <v>515221</v>
       </c>
       <c r="R97" t="n">
-        <v>6924414</v>
+        <v>6924386</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12100,7 +12100,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120318845</v>
+        <v>120318812</v>
       </c>
       <c r="B98" t="n">
         <v>97930</v>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12144,10 +12144,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>515553</v>
+        <v>515007</v>
       </c>
       <c r="R98" t="n">
-        <v>6924626</v>
+        <v>6924912</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12206,7 +12206,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120318818</v>
+        <v>120318830</v>
       </c>
       <c r="B99" t="n">
         <v>97930</v>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12250,10 +12250,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>514820</v>
+        <v>515149</v>
       </c>
       <c r="R99" t="n">
-        <v>6924711</v>
+        <v>6924307</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12312,7 +12312,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120318817</v>
+        <v>120318820</v>
       </c>
       <c r="B100" t="n">
         <v>97930</v>
@@ -12347,7 +12347,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12356,10 +12356,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>514849</v>
+        <v>514913</v>
       </c>
       <c r="R100" t="n">
-        <v>6924760</v>
+        <v>6924578</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120318846</v>
+        <v>120318845</v>
       </c>
       <c r="B101" t="n">
         <v>97930</v>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12462,10 +12462,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>515647</v>
+        <v>515553</v>
       </c>
       <c r="R101" t="n">
-        <v>6924817</v>
+        <v>6924626</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12524,7 +12524,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120318816</v>
+        <v>120318821</v>
       </c>
       <c r="B102" t="n">
         <v>97930</v>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -12568,10 +12568,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>514838</v>
+        <v>514957</v>
       </c>
       <c r="R102" t="n">
-        <v>6924796</v>
+        <v>6924623</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12630,7 +12630,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120318842</v>
+        <v>120318831</v>
       </c>
       <c r="B103" t="n">
         <v>97930</v>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12674,10 +12674,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>515405</v>
+        <v>515187</v>
       </c>
       <c r="R103" t="n">
-        <v>6924637</v>
+        <v>6924328</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120318819</v>
+        <v>120318841</v>
       </c>
       <c r="B104" t="n">
         <v>97930</v>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12780,10 +12780,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>514895</v>
+        <v>515403</v>
       </c>
       <c r="R104" t="n">
-        <v>6924584</v>
+        <v>6924623</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12842,7 +12842,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120318834</v>
+        <v>120318852</v>
       </c>
       <c r="B105" t="n">
         <v>97930</v>
@@ -12875,21 +12875,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>515221</v>
+        <v>515293</v>
       </c>
       <c r="R105" t="n">
-        <v>6924386</v>
+        <v>6925084</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12916,12 +12912,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12948,7 +12944,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120318828</v>
+        <v>120318837</v>
       </c>
       <c r="B106" t="n">
         <v>97930</v>
@@ -12983,7 +12979,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -12992,10 +12988,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>515127</v>
+        <v>515326</v>
       </c>
       <c r="R106" t="n">
-        <v>6924384</v>
+        <v>6924467</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13054,7 +13050,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120318825</v>
+        <v>120318844</v>
       </c>
       <c r="B107" t="n">
         <v>97930</v>
@@ -13089,7 +13085,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13098,10 +13094,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>515094</v>
+        <v>515557</v>
       </c>
       <c r="R107" t="n">
-        <v>6924722</v>
+        <v>6924620</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13160,7 +13156,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120318832</v>
+        <v>120318847</v>
       </c>
       <c r="B108" t="n">
         <v>97930</v>
@@ -13195,7 +13191,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -13204,10 +13200,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>515203</v>
+        <v>515636</v>
       </c>
       <c r="R108" t="n">
-        <v>6924357</v>
+        <v>6924856</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13266,7 +13262,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120318815</v>
+        <v>120318814</v>
       </c>
       <c r="B109" t="n">
         <v>97930</v>
@@ -13301,7 +13297,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>380</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -13310,10 +13306,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>514859</v>
+        <v>514909</v>
       </c>
       <c r="R109" t="n">
-        <v>6924782</v>
+        <v>6924793</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13372,7 +13368,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120318822</v>
+        <v>120318842</v>
       </c>
       <c r="B110" t="n">
         <v>97930</v>
@@ -13407,7 +13403,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13416,10 +13412,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>515056</v>
+        <v>515405</v>
       </c>
       <c r="R110" t="n">
-        <v>6924723</v>
+        <v>6924637</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13478,7 +13474,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120318844</v>
+        <v>120318818</v>
       </c>
       <c r="B111" t="n">
         <v>97930</v>
@@ -13513,7 +13509,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13522,10 +13518,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>515557</v>
+        <v>514820</v>
       </c>
       <c r="R111" t="n">
-        <v>6924620</v>
+        <v>6924711</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13584,7 +13580,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120318814</v>
+        <v>120318849</v>
       </c>
       <c r="B112" t="n">
         <v>97930</v>
@@ -13619,7 +13615,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -13628,10 +13624,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>514909</v>
+        <v>515497</v>
       </c>
       <c r="R112" t="n">
-        <v>6924793</v>
+        <v>6924983</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13690,7 +13686,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120318826</v>
+        <v>120318819</v>
       </c>
       <c r="B113" t="n">
         <v>97930</v>
@@ -13725,7 +13721,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13734,10 +13730,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>515119</v>
+        <v>514895</v>
       </c>
       <c r="R113" t="n">
-        <v>6924734</v>
+        <v>6924584</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13796,7 +13792,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120318848</v>
+        <v>120318813</v>
       </c>
       <c r="B114" t="n">
         <v>97930</v>
@@ -13831,7 +13827,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13840,10 +13836,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>515521</v>
+        <v>514992</v>
       </c>
       <c r="R114" t="n">
-        <v>6924943</v>
+        <v>6924909</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13902,7 +13898,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120318852</v>
+        <v>120318826</v>
       </c>
       <c r="B115" t="n">
         <v>97930</v>
@@ -13935,17 +13931,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>515293</v>
+        <v>515119</v>
       </c>
       <c r="R115" t="n">
-        <v>6925084</v>
+        <v>6924734</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13972,12 +13972,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -4032,12 +4032,7 @@
         <v>110815645</v>
       </c>
       <c r="B29" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91812</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4063,16 +4058,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Holmnäset, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515076.2852494456</v>
+        <v>515077</v>
       </c>
       <c r="R29" t="n">
-        <v>6924719.261247525</v>
+        <v>6924720</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4102,24 +4100,14 @@
           <t>2023-07-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-07-13</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På ~15 cm i diameter självgallrad tallåga med barken kvar. Tillsammans med gulporig ticka.</t>
+          <t>På ~15 cm i diameter självgallrad tallåga med barken kvar. Tillsammans med ostticka.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4128,6 +4116,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -4032,7 +4032,7 @@
         <v>110815645</v>
       </c>
       <c r="B29" t="n">
-        <v>91812</v>
+        <v>91814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carl Jansson, Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu, Carl Jansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -4032,7 +4032,7 @@
         <v>110815645</v>
       </c>
       <c r="B29" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu, Carl Jansson</t>
+          <t>Carl Jansson, Sebastian Kirppu, Karolin Hård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -4032,7 +4032,7 @@
         <v>110815645</v>
       </c>
       <c r="B29" t="n">
-        <v>91906</v>
+        <v>91918</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -4032,7 +4032,7 @@
         <v>110815645</v>
       </c>
       <c r="B29" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -4032,7 +4032,7 @@
         <v>110815645</v>
       </c>
       <c r="B29" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -4032,7 +4032,7 @@
         <v>110815645</v>
       </c>
       <c r="B29" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -4032,7 +4032,7 @@
         <v>110815645</v>
       </c>
       <c r="B29" t="n">
-        <v>91948</v>
+        <v>91958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -4032,7 +4032,7 @@
         <v>110815645</v>
       </c>
       <c r="B29" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -4032,7 +4032,7 @@
         <v>110815645</v>
       </c>
       <c r="B29" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 13495-2023 artfynd.xlsx
+++ b/artfynd/A 13495-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AZ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815661</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815663</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815668</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815664</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815666</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860523</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860524</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815685</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815678</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111609168</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1903,6 +1958,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815645</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2033,6 +2093,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815644</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2130,6 +2195,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815636</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2227,6 +2297,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815662</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2324,6 +2399,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815665</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2421,6 +2501,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815680</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2523,6 +2608,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860520</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2625,6 +2715,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860522</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2727,6 +2822,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875647</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2839,6 +2939,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815660</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2951,6 +3056,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815667</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3058,6 +3168,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860514</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3165,6 +3280,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860521</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3282,6 +3402,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815652</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3380,6 +3505,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875631</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3497,6 +3627,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815653</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3609,6 +3744,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815640</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3721,6 +3861,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815647</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3828,6 +3973,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860509</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3935,6 +4085,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875643</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4042,6 +4197,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875646</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4154,6 +4314,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815646</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4266,6 +4431,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815656</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4378,6 +4548,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815673</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4490,6 +4665,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815681</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4602,6 +4782,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815635</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4714,6 +4899,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815655</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4826,6 +5016,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815684</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4923,6 +5118,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815679</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5030,6 +5230,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860516</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5137,6 +5342,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860517</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5244,6 +5454,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860519</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5361,6 +5576,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815651</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5488,6 +5708,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815649</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5585,6 +5810,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815633</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5682,6 +5912,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815634</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5779,6 +6014,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815637</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5876,6 +6116,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815638</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5973,6 +6218,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815641</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6070,6 +6320,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815642</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6167,6 +6422,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815643</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6264,6 +6524,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815648</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6361,6 +6626,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815659</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6467,6 +6737,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860503</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6573,6 +6848,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860504</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6679,6 +6959,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860505</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6785,6 +7070,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860507</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6887,6 +7177,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860508</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6993,6 +7288,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860512</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7099,6 +7399,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860513</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7205,6 +7510,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860518</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7311,6 +7621,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875650</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7413,6 +7728,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875651</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7514,6 +7834,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318812</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7615,6 +7940,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318813</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7716,6 +8046,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318814</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7817,6 +8152,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318815</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7918,6 +8258,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318816</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8019,6 +8364,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318817</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8120,6 +8470,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318818</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8221,6 +8576,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318819</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8322,6 +8682,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318820</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8423,6 +8788,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318821</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8524,6 +8894,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318822</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8625,6 +9000,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318823</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8726,6 +9106,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318824</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8827,6 +9212,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318825</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8928,6 +9318,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318826</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9029,6 +9424,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318827</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9130,6 +9530,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318828</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9231,6 +9636,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318829</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9332,6 +9742,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318830</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9433,6 +9848,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318831</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9534,6 +9954,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318832</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9635,6 +10060,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318833</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9736,6 +10166,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318834</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9837,6 +10272,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318835</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9938,6 +10378,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318836</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10039,6 +10484,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318837</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10140,6 +10590,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318839</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10237,6 +10692,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318840</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10338,6 +10798,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318841</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10439,6 +10904,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318842</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10536,6 +11006,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318843</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10637,6 +11112,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318844</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10738,6 +11218,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318845</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10839,6 +11324,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318846</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10940,6 +11430,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318847</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11041,6 +11536,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318848</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11142,6 +11642,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318849</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11239,6 +11744,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318852</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11351,6 +11861,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815639</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11468,6 +11983,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815654</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11580,6 +12100,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815658</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11692,6 +12217,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815671</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11804,6 +12334,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815672</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11916,6 +12451,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815674</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12028,6 +12568,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815677</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12140,6 +12685,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815682</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12247,6 +12797,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860506</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12354,6 +12909,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860510</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12461,6 +13021,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110860515</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12568,6 +13133,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875642</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12675,6 +13245,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875645</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12792,8 +13367,130 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110815650</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>